--- a/diseases/d025/2005-2009.xlsx
+++ b/diseases/d025/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>33</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.6290408727884924</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>11</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>3.705768702761977</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>19</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.4109775121757496</v>
       </c>
@@ -2693,9 +2684,6 @@
       <c r="O13" t="n">
         <v>29</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.5527934942686752</v>
       </c>
@@ -3237,9 +3225,6 @@
       <c r="O16" t="n">
         <v>29</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.6272814659524598</v>
       </c>
@@ -3929,9 +3914,6 @@
       <c r="O20" t="n">
         <v>29</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.5527934942686752</v>
       </c>
@@ -4473,9 +4455,6 @@
       <c r="O23" t="n">
         <v>20</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.4326079075534207</v>
       </c>
@@ -5165,9 +5144,6 @@
       <c r="O27" t="n">
         <v>39</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.7434119405682184</v>
       </c>
@@ -5709,9 +5685,6 @@
       <c r="O30" t="n">
         <v>26</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5623902798194468</v>
       </c>
@@ -6401,9 +6374,6 @@
       <c r="O34" t="n">
         <v>40</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.7624737851981727</v>
       </c>
@@ -6945,9 +6915,6 @@
       <c r="O37" t="n">
         <v>20</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.4326079075534207</v>
       </c>
@@ -7637,9 +7604,6 @@
       <c r="O41" t="n">
         <v>32</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.6099790281585381</v>
       </c>
@@ -8181,9 +8145,6 @@
       <c r="O44" t="n">
         <v>21</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.4542383029310916</v>
       </c>
@@ -8873,9 +8834,6 @@
       <c r="O48" t="n">
         <v>27</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.5146698050087665</v>
       </c>
@@ -9417,9 +9375,6 @@
       <c r="O51" t="n">
         <v>21</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.4542383029310916</v>
       </c>
@@ -10109,9 +10064,6 @@
       <c r="O55" t="n">
         <v>25</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.4765461157488579</v>
       </c>
@@ -10653,9 +10605,6 @@
       <c r="O58" t="n">
         <v>25</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.5407598844417758</v>
       </c>
@@ -11345,9 +11294,6 @@
       <c r="O62" t="n">
         <v>40</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.7624737851981727</v>
       </c>
@@ -11889,9 +11835,6 @@
       <c r="O65" t="n">
         <v>27</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.5840206751971178</v>
       </c>
@@ -12581,9 +12524,6 @@
       <c r="O69" t="n">
         <v>27</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.5146698050087665</v>
       </c>
@@ -13125,9 +13065,6 @@
       <c r="O72" t="n">
         <v>18</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.3893471167980785</v>
       </c>
@@ -13817,9 +13754,6 @@
       <c r="O76" t="n">
         <v>35</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.667164562048401</v>
       </c>
@@ -14361,9 +14295,6 @@
       <c r="O79" t="n">
         <v>25</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.5407598844417758</v>
       </c>
@@ -15053,9 +14984,6 @@
       <c r="O83" t="n">
         <v>18</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.3431132033391777</v>
       </c>
@@ -15597,9 +15525,6 @@
       <c r="O86" t="n">
         <v>32</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.692172652085473</v>
       </c>
@@ -16289,9 +16214,6 @@
       <c r="O90" t="n">
         <v>28</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.5316879868802191</v>
       </c>
@@ -16833,9 +16755,6 @@
       <c r="O93" t="n">
         <v>13</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>4.278088944759999</v>
       </c>
@@ -17229,9 +17148,6 @@
       <c r="O95" t="n">
         <v>23</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.49350991547248</v>
       </c>
@@ -17921,9 +17837,6 @@
       <c r="O99" t="n">
         <v>27</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.5126991302059256</v>
       </c>
@@ -18465,9 +18378,6 @@
       <c r="O102" t="n">
         <v>27</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.5793377268589982</v>
       </c>
@@ -19157,9 +19067,6 @@
       <c r="O106" t="n">
         <v>29</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.5506768435545127</v>
       </c>
@@ -19701,9 +19608,6 @@
       <c r="O109" t="n">
         <v>25</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.5364238211657391</v>
       </c>
@@ -20393,9 +20297,6 @@
       <c r="O113" t="n">
         <v>26</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.4937102735316321</v>
       </c>
@@ -20937,9 +20838,6 @@
       <c r="O116" t="n">
         <v>23</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.49350991547248</v>
       </c>
@@ -21629,9 +21527,6 @@
       <c r="O120" t="n">
         <v>25</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.4747214168573385</v>
       </c>
@@ -22173,9 +22068,6 @@
       <c r="O123" t="n">
         <v>29</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.6222516325522573</v>
       </c>
@@ -22865,9 +22757,6 @@
       <c r="O127" t="n">
         <v>34</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.6456211269259804</v>
       </c>
@@ -23409,9 +23298,6 @@
       <c r="O130" t="n">
         <v>31</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.6651655382455165</v>
       </c>
@@ -24101,9 +23987,6 @@
       <c r="O134" t="n">
         <v>24</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.455732560183045</v>
       </c>
@@ -24645,9 +24528,6 @@
       <c r="O137" t="n">
         <v>26</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.5578807740123687</v>
       </c>
@@ -25337,9 +25217,6 @@
       <c r="O141" t="n">
         <v>19</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.3607882768115773</v>
       </c>
@@ -25881,9 +25758,6 @@
       <c r="O144" t="n">
         <v>18</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.3862251512393321</v>
       </c>
@@ -26573,9 +26447,6 @@
       <c r="O148" t="n">
         <v>30</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.5696657002288062</v>
       </c>
@@ -27117,9 +26988,6 @@
       <c r="O151" t="n">
         <v>19</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.4076821040859617</v>
       </c>
@@ -27809,9 +27677,6 @@
       <c r="O155" t="n">
         <v>27</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.5126991302059256</v>
       </c>
@@ -28353,9 +28218,6 @@
       <c r="O158" t="n">
         <v>28</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.6007946797056277</v>
       </c>
@@ -29045,9 +28907,6 @@
       <c r="O162" t="n">
         <v>15</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.2848328501144031</v>
       </c>
@@ -29589,9 +29448,6 @@
       <c r="O165" t="n">
         <v>21</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.4505960097792208</v>
       </c>
@@ -30281,9 +30137,6 @@
       <c r="O169" t="n">
         <v>13</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.2468551367658161</v>
       </c>
@@ -30825,9 +30678,6 @@
       <c r="O172" t="n">
         <v>20</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.4291390569325913</v>
       </c>
@@ -31517,9 +31367,6 @@
       <c r="O176" t="n">
         <v>35</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.661787089857451</v>
       </c>
@@ -32061,9 +31908,6 @@
       <c r="O179" t="n">
         <v>14</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>4.492211628089799</v>
       </c>
@@ -32457,9 +32301,6 @@
       <c r="O181" t="n">
         <v>38</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.8069636717696501</v>
       </c>
@@ -33149,9 +32990,6 @@
       <c r="O185" t="n">
         <v>29</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.5483378744533166</v>
       </c>
@@ -33693,9 +33531,6 @@
       <c r="O188" t="n">
         <v>22</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.4671894941824291</v>
       </c>
@@ -34385,9 +34220,6 @@
       <c r="O192" t="n">
         <v>38</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.7185116975595184</v>
       </c>
@@ -34929,9 +34761,6 @@
       <c r="O195" t="n">
         <v>23</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.4884253802816304</v>
       </c>
@@ -35621,9 +35450,6 @@
       <c r="O199" t="n">
         <v>23</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.4348886590491821</v>
       </c>
@@ -36165,9 +35991,6 @@
       <c r="O202" t="n">
         <v>15</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.3185382914880198</v>
       </c>
@@ -36857,9 +36680,6 @@
       <c r="O206" t="n">
         <v>30</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.5672460770206723</v>
       </c>
@@ -37401,9 +37221,6 @@
       <c r="O209" t="n">
         <v>24</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.5096612663808316</v>
       </c>
@@ -38093,9 +37910,6 @@
       <c r="O213" t="n">
         <v>42</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.7941445078289413</v>
       </c>
@@ -38637,9 +38451,6 @@
       <c r="O216" t="n">
         <v>24</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.5096612663808316</v>
       </c>
@@ -39329,9 +39140,6 @@
       <c r="O220" t="n">
         <v>22</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.4159804564818264</v>
       </c>
@@ -39873,9 +39681,6 @@
       <c r="O223" t="n">
         <v>24</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.5096612663808316</v>
       </c>
@@ -40565,9 +40370,6 @@
       <c r="O227" t="n">
         <v>36</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.6806952924248069</v>
       </c>
@@ -41109,9 +40911,6 @@
       <c r="O230" t="n">
         <v>19</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.4034818358848251</v>
       </c>
@@ -41801,9 +41600,6 @@
       <c r="O234" t="n">
         <v>21</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.3970722539144707</v>
       </c>
@@ -42345,9 +42141,6 @@
       <c r="O237" t="n">
         <v>27</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.5733689246784356</v>
       </c>
@@ -43037,9 +42830,6 @@
       <c r="O241" t="n">
         <v>26</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.4916132667512493</v>
       </c>
@@ -43581,9 +43371,6 @@
       <c r="O244" t="n">
         <v>31</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.6583124690752409</v>
       </c>
@@ -44273,9 +44060,6 @@
       <c r="O248" t="n">
         <v>28</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.5294296718859608</v>
       </c>
@@ -44817,9 +44601,6 @@
       <c r="O251" t="n">
         <v>30</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.6370765829760395</v>
       </c>
@@ -45509,9 +45290,6 @@
       <c r="O255" t="n">
         <v>17</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.3214394436450477</v>
       </c>
@@ -46053,9 +45831,6 @@
       <c r="O258" t="n">
         <v>25</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.5308971524800329</v>
       </c>
@@ -46745,9 +46520,6 @@
       <c r="O262" t="n">
         <v>29</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.5457922522719544</v>
       </c>
@@ -47289,9 +47061,6 @@
       <c r="O265" t="n">
         <v>6</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>1.889677479296221</v>
       </c>
@@ -47685,9 +47454,6 @@
       <c r="O267" t="n">
         <v>23</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.4823723322974912</v>
       </c>
@@ -48377,9 +48143,6 @@
       <c r="O271" t="n">
         <v>21</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.3952288723348635</v>
       </c>
@@ -48921,9 +48684,6 @@
       <c r="O274" t="n">
         <v>23</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.4823723322974912</v>
       </c>
@@ -49613,9 +49373,6 @@
       <c r="O278" t="n">
         <v>18</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.3387676048584544</v>
       </c>
@@ -50157,9 +49914,6 @@
       <c r="O281" t="n">
         <v>25</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.5243177524972731</v>
       </c>
@@ -50849,9 +50603,6 @@
       <c r="O285" t="n">
         <v>29</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.5457922522719544</v>
       </c>
@@ -51393,9 +51144,6 @@
       <c r="O288" t="n">
         <v>33</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.6920994332964003</v>
       </c>
@@ -52085,9 +51833,6 @@
       <c r="O292" t="n">
         <v>33</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.6210739422404997</v>
       </c>
@@ -52629,9 +52374,6 @@
       <c r="O295" t="n">
         <v>27</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.5662631726970548</v>
       </c>
@@ -53321,9 +53063,6 @@
       <c r="O299" t="n">
         <v>33</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.6210739422404997</v>
       </c>
@@ -53865,9 +53604,6 @@
       <c r="O302" t="n">
         <v>35</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.7340448534961822</v>
       </c>
@@ -54557,9 +54293,6 @@
       <c r="O306" t="n">
         <v>28</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.5269718297798179</v>
       </c>
@@ -55101,9 +54834,6 @@
       <c r="O309" t="n">
         <v>30</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.6291813029967276</v>
       </c>
@@ -55793,9 +55523,6 @@
       <c r="O313" t="n">
         <v>40</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.7528168996854543</v>
       </c>
@@ -56337,9 +56064,6 @@
       <c r="O316" t="n">
         <v>25</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.5243177524972731</v>
       </c>
@@ -57029,9 +56753,6 @@
       <c r="O320" t="n">
         <v>26</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.4893309847955453</v>
       </c>
@@ -57573,9 +57294,6 @@
       <c r="O323" t="n">
         <v>24</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.5033450423973821</v>
       </c>
@@ -58265,9 +57983,6 @@
       <c r="O327" t="n">
         <v>35</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.6587147872247725</v>
       </c>
@@ -58809,9 +58524,6 @@
       <c r="O330" t="n">
         <v>20</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.4194542019978185</v>
       </c>
@@ -59501,9 +59213,6 @@
       <c r="O334" t="n">
         <v>25</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.4705105623034089</v>
       </c>
@@ -60045,9 +59754,6 @@
       <c r="O337" t="n">
         <v>25</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.5243177524972731</v>
       </c>
@@ -60737,9 +60443,6 @@
       <c r="O341" t="n">
         <v>24</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.4516901398112726</v>
       </c>
@@ -61281,9 +60984,6 @@
       <c r="O344" t="n">
         <v>23</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.4823723322974912</v>
       </c>
@@ -61973,9 +61673,6 @@
       <c r="O348" t="n">
         <v>32</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.5993792865569622</v>
       </c>
@@ -62517,9 +62214,6 @@
       <c r="O351" t="n">
         <v>9</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>2.824752363376144</v>
       </c>
@@ -62913,9 +62607,6 @@
       <c r="O353" t="n">
         <v>20</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.4141968025042339</v>
       </c>
@@ -63605,9 +63296,6 @@
       <c r="O357" t="n">
         <v>36</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.6743016973765824</v>
       </c>
@@ -64149,9 +63837,6 @@
       <c r="O360" t="n">
         <v>23</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.4763263228798689</v>
       </c>
@@ -64841,9 +64526,6 @@
       <c r="O364" t="n">
         <v>39</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.7304935054912977</v>
       </c>
@@ -65385,9 +65067,6 @@
       <c r="O367" t="n">
         <v>28</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0.5798755235059274</v>
       </c>
@@ -66077,9 +65756,6 @@
       <c r="O371" t="n">
         <v>43</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.8054159163109178</v>
       </c>
@@ -66621,9 +66297,6 @@
       <c r="O374" t="n">
         <v>30</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.6212952037563508</v>
       </c>
@@ -67313,9 +66986,6 @@
       <c r="O378" t="n">
         <v>38</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0.7117629027863926</v>
       </c>
@@ -67857,9 +67527,6 @@
       <c r="O381" t="n">
         <v>44</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.9112329655093145</v>
       </c>
@@ -68549,9 +68216,6 @@
       <c r="O385" t="n">
         <v>40</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.7492241081962028</v>
       </c>
@@ -69093,9 +68757,6 @@
       <c r="O388" t="n">
         <v>43</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0.8905231253841028</v>
       </c>
@@ -69785,9 +69446,6 @@
       <c r="O392" t="n">
         <v>41</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.7679547109011077</v>
       </c>
@@ -70329,9 +69987,6 @@
       <c r="O395" t="n">
         <v>14</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0.2899377617529637</v>
       </c>
@@ -71021,9 +70676,6 @@
       <c r="O399" t="n">
         <v>40</v>
       </c>
-      <c r="Q399" t="n">
-        <v>0</v>
-      </c>
       <c r="R399" t="n">
         <v>0.7492241081962028</v>
       </c>
@@ -71565,9 +71217,6 @@
       <c r="O402" t="n">
         <v>37</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0.7662640846328327</v>
       </c>
@@ -72257,9 +71906,6 @@
       <c r="O406" t="n">
         <v>21</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.3933426568030064</v>
       </c>
@@ -72801,9 +72447,6 @@
       <c r="O409" t="n">
         <v>33</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.6834247241319859</v>
       </c>
@@ -73493,9 +73136,6 @@
       <c r="O413" t="n">
         <v>31</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.580648683852057</v>
       </c>
@@ -74037,9 +73677,6 @@
       <c r="O416" t="n">
         <v>31</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.6420050438815624</v>
       </c>
@@ -74729,9 +74366,6 @@
       <c r="O420" t="n">
         <v>30</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0.561918081147152</v>
       </c>
@@ -75273,9 +74907,6 @@
       <c r="O423" t="n">
         <v>27</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0.5591656833807157</v>
       </c>
@@ -75965,9 +75596,6 @@
       <c r="O427" t="n">
         <v>27</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.5057262730324368</v>
       </c>
@@ -76508,9 +76136,6 @@
       </c>
       <c r="O430" t="n">
         <v>28</v>
-      </c>
-      <c r="Q430" t="n">
-        <v>0</v>
       </c>
       <c r="R430" t="n">
         <v>0.5798755235059274</v>
